--- a/redmine-logger/backend/timelog.xlsx
+++ b/redmine-logger/backend/timelog.xlsx
@@ -32,10 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -400,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D67"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -424,7 +423,7 @@
         <v>158484</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="str">
         <v>YTP - LA height and weight entered details  are not appearing after recalculating BI from Review Details screen and the Make Payment screen.</v>
@@ -438,7 +437,7 @@
         <v>158484</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="str">
         <v>CM/FT logic is not working for the spouse screen</v>
@@ -452,7 +451,7 @@
         <v>158484</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1" t="str">
         <v>In YTP height detail is showing as “NA” on the Review Details screen.</v>
@@ -466,7 +465,7 @@
         <v>158484</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="str">
         <v>annur journey is completed still Proceed now is displayed on the screen to procced again for  annur</v>
@@ -480,24 +479,24 @@
         <v>158484</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="str">
-        <v>Like sone screen header content is - Employer details , e-insurance account details ---(not clear this for la or pr)</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B7" s="1">
         <v>158484</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Like sone screen header content is - Employer details , e-insurance account details ---(not clear this for la or pr)</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -508,7 +507,7 @@
         <v>158484</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1" t="str" xml:space="preserve">
         <v xml:space="preserve">Photo Alignment Issue
@@ -523,7 +522,7 @@
         <v>158484</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="str" xml:space="preserve">
         <v xml:space="preserve">SP Code Missing
@@ -538,38 +537,38 @@
         <v>158484</v>
       </c>
       <c r="C10" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="str">
-        <v>On the Review details screen header and below section not clear this is for la or pr</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="B11" s="1">
         <v>158484</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1" t="str">
-        <v>After recalculate -The Bank Name and Bank Branch Name data vanished after recalculate BI</v>
+        <v>On the Review details screen header and below section not clear this is for la or pr</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="B12" s="1">
         <v>158484</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>After recalculate -The Bank Name and Bank Branch Name data vanished after recalculate BI</v>
       </c>
     </row>
     <row r="13">
@@ -580,43 +579,43 @@
         <v>158484</v>
       </c>
       <c r="C13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="str">
-        <v>Under nominee, PA section basis pin code state and city details are not auto-fetched.</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B14" s="1">
         <v>158484</v>
       </c>
       <c r="C14" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1" t="str">
-        <v>API wrapper App Number Duplicate Check</v>
+        <v>Under nominee, PA section basis pin code state and city details are not auto-fetched.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B15" s="1">
         <v>158484</v>
       </c>
       <c r="C15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="1" t="str">
-        <v>API wrapper ANUR PIVC Link Generation</v>
+        <v>API wrapper App Number Duplicate Check</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B16" s="1">
         <v>158484</v>
@@ -625,7 +624,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>API wrapper ANUR PIVC Link Generation</v>
       </c>
     </row>
     <row r="17">
@@ -636,7 +635,7 @@
         <v>158484</v>
       </c>
       <c r="C17" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="1" t="str">
         <v>API wrapper Filenet DMS</v>
@@ -650,24 +649,24 @@
         <v>158484</v>
       </c>
       <c r="C18" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="1" t="str">
-        <v>API wrapper Medical Scheduling / checkTPA</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B19" s="1">
         <v>158484</v>
       </c>
       <c r="C19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>API wrapper Medical Scheduling / checkTPA</v>
       </c>
     </row>
     <row r="20">
@@ -678,7 +677,7 @@
         <v>158484</v>
       </c>
       <c r="C20" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="str">
         <v>API wrapper generate-bi</v>
@@ -692,7 +691,7 @@
         <v>158484</v>
       </c>
       <c r="C21" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="1" t="str">
         <v>App Number Duplicate Check</v>
@@ -734,7 +733,7 @@
         <v>158484</v>
       </c>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="1" t="str">
         <v>Unified Proposal API</v>
@@ -762,7 +761,7 @@
         <v>158484</v>
       </c>
       <c r="C26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="1" t="str">
         <v>ANUR PIVC Link Generation</v>
@@ -776,24 +775,24 @@
         <v>158484</v>
       </c>
       <c r="C27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="1" t="str">
-        <v>Filenet DMS</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B28" s="1">
         <v>158484</v>
       </c>
       <c r="C28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Filenet DMS</v>
       </c>
     </row>
     <row r="29">
@@ -804,43 +803,43 @@
         <v>158484</v>
       </c>
       <c r="C29" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" s="1" t="str">
-        <v>Leave</v>
+        <v>Medical Scheduling / checkTPA</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B30" s="1">
         <v>158484</v>
       </c>
       <c r="C30" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D30" s="1" t="str">
-        <v>Leave</v>
+        <v>Merge branch 'insure/develop' into insure2.0/secureInvest</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B31" s="1">
         <v>158484</v>
       </c>
       <c r="C31" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D31" s="1" t="str">
-        <v>Leave</v>
+        <v>add</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B32" s="1">
         <v>158484</v>
@@ -849,26 +848,502 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="str">
-        <v>Medical Scheduling / checkTPA</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="B33" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C33" s="1">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <v>add</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="B34" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="str">
+        <v>secureInvest-riderAdded</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="B35" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="str">
+        <v>inital structure ready</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="B36" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B37" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="str">
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B38" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="str">
+        <v>ComponentCmpTagToggleSwitch fix</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B39" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="str">
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B40" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1" t="str">
+        <v>staff discount key fix</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B41" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="str">
         <v>2026-04-14</v>
       </c>
-      <c r="B33" s="1">
-        <v>158484</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="str">
+      <c r="B42" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="str">
+        <v>changemedicalquestionvalue</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B43" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1" t="str">
+        <v>Merge branch 'pennydropIntegration' into insure/develop</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B44" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <v>penny drop api integration</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B45" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B46" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C46" s="1">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B47" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <v>upload proceed now bg color fix</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B48" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <v>upload proceed now bg color fix</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B49" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="str">
+        <v>for EQUITAS no setIsLaMinor check</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B50" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B51" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <v>Merge remote-tracking branch 'origin/CR-36689-sgp' into smartGuaranteedPension-frontend</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B52" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <v>SGP dynamic heading restore</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B53" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <v>Merge branch 'CR-36689-cpf' into secureInvestPlan-frontend</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B54" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1</v>
+      </c>
+      <c r="D54" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B55" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C55" s="1">
+        <v>4</v>
+      </c>
+      <c r="D55" s="1" t="str">
+        <v>Merge branch 'CR-36689-ytp' into youngTermPlan-frontend</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B56" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C56" s="1">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <v>Merge branch 'smartGuaranteedPension-frontend' of https://github.com/lumiqai/ISNP into smartGuaranteedPension-frontend</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B57" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+      <c r="D57" s="1" t="str">
+        <v>Merge branch 'CR-36689-sgp' into smartGuaranteedPension-frontend</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B58" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B59" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C59" s="1">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <v>Merge branch 'CR-36689-sgp' of https://github.com/lumiqai/ISNP into CR-36689-sgp</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B60" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1" t="str">
+        <v>dynamic heading added for nomiee</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B61" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <v>Merge branch 'CR-36689-sgp' into smartGuaranteedPension-frontend</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B62" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <v>Merge branch 'CR-36689-ytp' into youngTermPlan-frontend</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B63" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B64" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="str">
+        <v>Merge branch 'CR-36689-cpf' into promise4LifePlan-frontend</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B65" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C65" s="1">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="str">
+        <v>Merge branch 'CR-36689-cpf' into promise4FuturePlan-frontend</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B66" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1" t="str">
+        <v>Merge branch 'CR-36689-cpf' into igfp-frontend</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B67" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D67"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/redmine-logger/backend/timelog.xlsx
+++ b/redmine-logger/backend/timelog.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -423,7 +423,7 @@
         <v>158484</v>
       </c>
       <c r="C2" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="str">
         <v>YTP - LA height and weight entered details  are not appearing after recalculating BI from Review Details screen and the Make Payment screen.</v>
@@ -437,7 +437,7 @@
         <v>158484</v>
       </c>
       <c r="C3" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1" t="str">
         <v>CM/FT logic is not working for the spouse screen</v>
@@ -451,7 +451,7 @@
         <v>158484</v>
       </c>
       <c r="C4" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="str">
         <v>In YTP height detail is showing as “NA” on the Review Details screen.</v>
@@ -507,14 +507,14 @@
         <v>158484</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1" t="str" xml:space="preserve">
         <v xml:space="preserve">Photo Alignment Issue
 There is an alignment issue on the first page of the proposal form caused by the photo size.</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
+    <row r="9">
       <c r="A9" s="1" t="str">
         <v>2026-04-02</v>
       </c>
@@ -524,23 +524,23 @@
       <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" s="1" t="str" xml:space="preserve">
+      <c r="D9" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" s="1" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="B10" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="str" xml:space="preserve">
         <v xml:space="preserve">SP Code Missing
 The SP code is not being populated in the proposal form first page.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="B10" s="1">
-        <v>158484</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="str">
-        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         <v>158484</v>
       </c>
       <c r="C11" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="str">
         <v>On the Review details screen header and below section not clear this is for la or pr</v>
@@ -565,7 +565,7 @@
         <v>158484</v>
       </c>
       <c r="C12" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1" t="str">
         <v>After recalculate -The Bank Name and Bank Branch Name data vanished after recalculate BI</v>
@@ -579,38 +579,38 @@
         <v>158484</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Under nominee, PA section basis pin code state and city details are not auto-fetched.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-03</v>
       </c>
       <c r="B14" s="1">
         <v>158484</v>
       </c>
       <c r="C14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="1" t="str">
-        <v>Under nominee, PA section basis pin code state and city details are not auto-fetched.</v>
+        <v>API wrapper App Number Duplicate Check</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-03</v>
       </c>
       <c r="B15" s="1">
         <v>158484</v>
       </c>
       <c r="C15" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="1" t="str">
-        <v>API wrapper App Number Duplicate Check</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +635,7 @@
         <v>158484</v>
       </c>
       <c r="C17" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1" t="str">
         <v>API wrapper Filenet DMS</v>
@@ -649,38 +649,38 @@
         <v>158484</v>
       </c>
       <c r="C18" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>API wrapper Medical Scheduling / checkTPA</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B19" s="1">
         <v>158484</v>
       </c>
       <c r="C19" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="1" t="str">
-        <v>API wrapper Medical Scheduling / checkTPA</v>
+        <v>API wrapper generate-bi</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B20" s="1">
         <v>158484</v>
       </c>
       <c r="C20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1" t="str">
-        <v>API wrapper generate-bi</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="21">
@@ -691,7 +691,7 @@
         <v>158484</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1" t="str">
         <v>App Number Duplicate Check</v>
@@ -705,7 +705,7 @@
         <v>158484</v>
       </c>
       <c r="C22" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="1" t="str">
         <v>Penny Drop Bank Validation</v>
@@ -733,7 +733,7 @@
         <v>158484</v>
       </c>
       <c r="C24" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" s="1" t="str">
         <v>Unified Proposal API</v>
@@ -747,7 +747,7 @@
         <v>158484</v>
       </c>
       <c r="C25" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="1" t="str">
         <v>App Number Duplicate Check</v>
@@ -761,7 +761,7 @@
         <v>158484</v>
       </c>
       <c r="C26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="1" t="str">
         <v>ANUR PIVC Link Generation</v>
@@ -789,7 +789,7 @@
         <v>158484</v>
       </c>
       <c r="C28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="1" t="str">
         <v>Filenet DMS</v>
@@ -803,7 +803,7 @@
         <v>158484</v>
       </c>
       <c r="C29" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" s="1" t="str">
         <v>Medical Scheduling / checkTPA</v>
@@ -817,7 +817,7 @@
         <v>158484</v>
       </c>
       <c r="C30" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1" t="str">
         <v>Merge branch 'insure/develop' into insure2.0/secureInvest</v>
@@ -831,7 +831,7 @@
         <v>158484</v>
       </c>
       <c r="C31" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" s="1" t="str">
         <v>add</v>
@@ -859,7 +859,7 @@
         <v>158484</v>
       </c>
       <c r="C33" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1" t="str">
         <v>add</v>
@@ -873,7 +873,7 @@
         <v>158484</v>
       </c>
       <c r="C34" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="1" t="str">
         <v>secureInvest-riderAdded</v>
@@ -887,7 +887,7 @@
         <v>158484</v>
       </c>
       <c r="C35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="1" t="str">
         <v>inital structure ready</v>
@@ -901,24 +901,24 @@
         <v>158484</v>
       </c>
       <c r="C36" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B37" s="1">
         <v>158484</v>
       </c>
       <c r="C37" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" s="1" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="38">
@@ -929,7 +929,7 @@
         <v>158484</v>
       </c>
       <c r="C38" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" s="1" t="str">
         <v>ComponentCmpTagToggleSwitch fix</v>
@@ -943,7 +943,7 @@
         <v>158484</v>
       </c>
       <c r="C39" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" s="1" t="str">
         <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
@@ -957,7 +957,7 @@
         <v>158484</v>
       </c>
       <c r="C40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="1" t="str">
         <v>staff discount key fix</v>
@@ -974,21 +974,21 @@
         <v>1</v>
       </c>
       <c r="D41" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>changemedicalquestionvalue</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-13</v>
       </c>
       <c r="B42" s="1">
         <v>158484</v>
       </c>
       <c r="C42" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" s="1" t="str">
-        <v>changemedicalquestionvalue</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="43">
@@ -999,7 +999,7 @@
         <v>158484</v>
       </c>
       <c r="C43" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" s="1" t="str">
         <v>Merge branch 'pennydropIntegration' into insure/develop</v>
@@ -1013,7 +1013,7 @@
         <v>158484</v>
       </c>
       <c r="C44" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" s="1" t="str">
         <v>penny drop api integration</v>
@@ -1027,38 +1027,38 @@
         <v>158484</v>
       </c>
       <c r="C45" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B46" s="1">
         <v>158484</v>
       </c>
       <c r="C46" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" s="1" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+        <v>upload proceed now bg color fix</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B47" s="1">
         <v>158484</v>
       </c>
       <c r="C47" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="1" t="str">
-        <v>upload proceed now bg color fix</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="48">
@@ -1069,7 +1069,7 @@
         <v>158484</v>
       </c>
       <c r="C48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="1" t="str">
         <v>upload proceed now bg color fix</v>
@@ -1083,7 +1083,7 @@
         <v>158484</v>
       </c>
       <c r="C49" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49" s="1" t="str">
         <v>for EQUITAS no setIsLaMinor check</v>
@@ -1097,24 +1097,24 @@
         <v>158484</v>
       </c>
       <c r="C50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge remote-tracking branch 'origin/CR-36689-sgp' into smartGuaranteedPension-frontend</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-15</v>
       </c>
       <c r="B51" s="1">
         <v>158484</v>
       </c>
       <c r="C51" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" s="1" t="str">
-        <v>Merge remote-tracking branch 'origin/CR-36689-sgp' into smartGuaranteedPension-frontend</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="52">
@@ -1153,24 +1153,24 @@
         <v>158484</v>
       </c>
       <c r="C54" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge branch 'CR-36689-ytp' into youngTermPlan-frontend</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-16</v>
       </c>
       <c r="B55" s="1">
         <v>158484</v>
       </c>
       <c r="C55" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" s="1" t="str">
-        <v>Merge branch 'CR-36689-ytp' into youngTermPlan-frontend</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="56">
@@ -1181,7 +1181,7 @@
         <v>158484</v>
       </c>
       <c r="C56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" s="1" t="str">
         <v>Merge branch 'smartGuaranteedPension-frontend' of https://github.com/lumiqai/ISNP into smartGuaranteedPension-frontend</v>
@@ -1195,7 +1195,7 @@
         <v>158484</v>
       </c>
       <c r="C57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="1" t="str">
         <v>Merge branch 'CR-36689-sgp' into smartGuaranteedPension-frontend</v>
@@ -1212,26 +1212,26 @@
         <v>1</v>
       </c>
       <c r="D58" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge branch 'CR-36689-sgp' of https://github.com/lumiqai/ISNP into CR-36689-sgp</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-17</v>
       </c>
       <c r="B59" s="1">
         <v>158484</v>
       </c>
       <c r="C59" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" s="1" t="str">
-        <v>Merge branch 'CR-36689-sgp' of https://github.com/lumiqai/ISNP into CR-36689-sgp</v>
+        <v>dynamic heading added for nomiee</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-17</v>
       </c>
       <c r="B60" s="1">
         <v>158484</v>
@@ -1240,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="1" t="str">
-        <v>dynamic heading added for nomiee</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="61">
@@ -1251,7 +1251,7 @@
         <v>158484</v>
       </c>
       <c r="C61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" s="1" t="str">
         <v>Merge branch 'CR-36689-sgp' into smartGuaranteedPension-frontend</v>
@@ -1279,24 +1279,24 @@
         <v>158484</v>
       </c>
       <c r="C63" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge branch 'CR-36689-cpf' into promise4LifePlan-frontend</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-20</v>
       </c>
       <c r="B64" s="1">
         <v>158484</v>
       </c>
       <c r="C64" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" s="1" t="str">
-        <v>Merge branch 'CR-36689-cpf' into promise4LifePlan-frontend</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="65">
@@ -1307,7 +1307,7 @@
         <v>158484</v>
       </c>
       <c r="C65" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" s="1" t="str">
         <v>Merge branch 'CR-36689-cpf' into promise4FuturePlan-frontend</v>
@@ -1321,7 +1321,7 @@
         <v>158484</v>
       </c>
       <c r="C66" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" s="1" t="str">
         <v>Merge branch 'CR-36689-cpf' into igfp-frontend</v>
@@ -1338,12 +1338,26 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="str">
+        <v>Merge branch 'CR-36689-cpf' into titaniumPlusPlan-frontend</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B68" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D68"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/redmine-logger/backend/timelog.xlsx
+++ b/redmine-logger/backend/timelog.xlsx
@@ -423,7 +423,7 @@
         <v>158484</v>
       </c>
       <c r="C2" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="str">
         <v>YTP - LA height and weight entered details  are not appearing after recalculating BI from Review Details screen and the Make Payment screen.</v>
@@ -468,21 +468,21 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>annur journey is completed still Proceed now is displayed on the screen to procced again for  annur</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B6" s="1">
         <v>158484</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>annur journey is completed still Proceed now is displayed on the screen to procced again for  annur</v>
       </c>
     </row>
     <row r="7">
@@ -493,7 +493,7 @@
         <v>158484</v>
       </c>
       <c r="C7" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="str">
         <v>Like sone screen header content is - Employer details , e-insurance account details ---(not clear this for la or pr)</v>
@@ -507,14 +507,14 @@
         <v>158484</v>
       </c>
       <c r="C8" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="str" xml:space="preserve">
         <v xml:space="preserve">Photo Alignment Issue
 There is an alignment issue on the first page of the proposal form caused by the photo size.</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" xml:space="preserve">
       <c r="A9" s="1" t="str">
         <v>2026-04-02</v>
       </c>
@@ -522,25 +522,25 @@
         <v>158484</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" s="1" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="B10" s="1">
-        <v>158484</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="str" xml:space="preserve">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="str" xml:space="preserve">
         <v xml:space="preserve">SP Code Missing
 The SP code is not being populated in the proposal form first page.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B10" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         <v>158484</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="1" t="str">
         <v>On the Review details screen header and below section not clear this is for la or pr</v>
@@ -565,7 +565,7 @@
         <v>158484</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="1" t="str">
         <v>After recalculate -The Bank Name and Bank Branch Name data vanished after recalculate BI</v>
@@ -593,7 +593,7 @@
         <v>158484</v>
       </c>
       <c r="C14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1" t="str">
         <v>API wrapper App Number Duplicate Check</v>
@@ -621,7 +621,7 @@
         <v>158484</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="1" t="str">
         <v>API wrapper ANUR PIVC Link Generation</v>
@@ -635,7 +635,7 @@
         <v>158484</v>
       </c>
       <c r="C17" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1" t="str">
         <v>API wrapper Filenet DMS</v>
@@ -649,7 +649,7 @@
         <v>158484</v>
       </c>
       <c r="C18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="1" t="str">
         <v>API wrapper Medical Scheduling / checkTPA</v>
@@ -666,21 +666,21 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="str">
-        <v>API wrapper generate-bi</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B20" s="1">
         <v>158484</v>
       </c>
       <c r="C20" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>API wrapper generate-bi</v>
       </c>
     </row>
     <row r="21">
@@ -705,7 +705,7 @@
         <v>158484</v>
       </c>
       <c r="C22" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="1" t="str">
         <v>Penny Drop Bank Validation</v>
@@ -747,7 +747,7 @@
         <v>158484</v>
       </c>
       <c r="C25" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="1" t="str">
         <v>App Number Duplicate Check</v>
@@ -761,7 +761,7 @@
         <v>158484</v>
       </c>
       <c r="C26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="1" t="str">
         <v>ANUR PIVC Link Generation</v>
@@ -789,7 +789,7 @@
         <v>158484</v>
       </c>
       <c r="C28" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="1" t="str">
         <v>Filenet DMS</v>
@@ -803,7 +803,7 @@
         <v>158484</v>
       </c>
       <c r="C29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="1" t="str">
         <v>Medical Scheduling / checkTPA</v>
@@ -817,7 +817,7 @@
         <v>158484</v>
       </c>
       <c r="C30" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="1" t="str">
         <v>Merge branch 'insure/develop' into insure2.0/secureInvest</v>
@@ -831,24 +831,24 @@
         <v>158484</v>
       </c>
       <c r="C31" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" s="1" t="str">
-        <v>add</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B32" s="1">
         <v>158484</v>
       </c>
       <c r="C32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>add</v>
       </c>
     </row>
     <row r="33">
@@ -859,7 +859,7 @@
         <v>158484</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="1" t="str">
         <v>add</v>
@@ -873,7 +873,7 @@
         <v>158484</v>
       </c>
       <c r="C34" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" s="1" t="str">
         <v>secureInvest-riderAdded</v>
@@ -890,12 +890,12 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>inital structure ready</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-13</v>
       </c>
       <c r="B36" s="1">
         <v>158484</v>
@@ -904,21 +904,21 @@
         <v>4</v>
       </c>
       <c r="D36" s="1" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+        <v>inital structure ready</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-13</v>
       </c>
       <c r="B37" s="1">
         <v>158484</v>
       </c>
       <c r="C37" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
     <row r="38">
@@ -943,52 +943,52 @@
         <v>158484</v>
       </c>
       <c r="C39" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D39" s="1" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B40" s="1">
         <v>158484</v>
       </c>
       <c r="C40" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" s="1" t="str">
-        <v>staff discount key fix</v>
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B41" s="1">
         <v>158484</v>
       </c>
       <c r="C41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="1" t="str">
-        <v>changemedicalquestionvalue</v>
+        <v>staff discount key fix</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B42" s="1">
         <v>158484</v>
       </c>
       <c r="C42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>changemedicalquestionvalue</v>
       </c>
     </row>
     <row r="43">
@@ -999,57 +999,57 @@
         <v>158484</v>
       </c>
       <c r="C43" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" s="1" t="str">
-        <v>Merge branch 'pennydropIntegration' into insure/develop</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-15</v>
       </c>
       <c r="B44" s="1">
         <v>158484</v>
       </c>
       <c r="C44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="1" t="str">
-        <v>penny drop api integration</v>
+        <v>Merge branch 'pennydropIntegration' into insure/develop</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-15</v>
       </c>
       <c r="B45" s="1">
         <v>158484</v>
       </c>
       <c r="C45" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" s="1" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+        <v>penny drop api integration</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-15</v>
       </c>
       <c r="B46" s="1">
         <v>158484</v>
       </c>
       <c r="C46" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" s="1" t="str">
-        <v>upload proceed now bg color fix</v>
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-15</v>
       </c>
       <c r="B47" s="1">
         <v>158484</v>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>upload proceed now bg color fix</v>
       </c>
     </row>
     <row r="48">
@@ -1069,7 +1069,7 @@
         <v>158484</v>
       </c>
       <c r="C48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" s="1" t="str">
         <v>upload proceed now bg color fix</v>
@@ -1083,38 +1083,38 @@
         <v>158484</v>
       </c>
       <c r="C49" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49" s="1" t="str">
-        <v>for EQUITAS no setIsLaMinor check</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="B50" s="1">
         <v>158484</v>
       </c>
       <c r="C50" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="1" t="str">
-        <v>Merge remote-tracking branch 'origin/CR-36689-sgp' into smartGuaranteedPension-frontend</v>
+        <v>for EQUITAS no setIsLaMinor check</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="B51" s="1">
         <v>158484</v>
       </c>
       <c r="C51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Merge remote-tracking branch 'origin/CR-36689-sgp' into smartGuaranteedPension-frontend</v>
       </c>
     </row>
     <row r="52">
@@ -1125,7 +1125,7 @@
         <v>158484</v>
       </c>
       <c r="C52" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" s="1" t="str">
         <v>SGP dynamic heading restore</v>
@@ -1139,7 +1139,7 @@
         <v>158484</v>
       </c>
       <c r="C53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="1" t="str">
         <v>Merge branch 'CR-36689-cpf' into secureInvestPlan-frontend</v>
@@ -1153,7 +1153,7 @@
         <v>158484</v>
       </c>
       <c r="C54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54" s="1" t="str">
         <v>Merge branch 'CR-36689-ytp' into youngTermPlan-frontend</v>
@@ -1181,7 +1181,7 @@
         <v>158484</v>
       </c>
       <c r="C56" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56" s="1" t="str">
         <v>Merge branch 'smartGuaranteedPension-frontend' of https://github.com/lumiqai/ISNP into smartGuaranteedPension-frontend</v>
@@ -1209,7 +1209,7 @@
         <v>158484</v>
       </c>
       <c r="C58" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" s="1" t="str">
         <v>Merge branch 'CR-36689-sgp' of https://github.com/lumiqai/ISNP into CR-36689-sgp</v>
@@ -1226,21 +1226,21 @@
         <v>1</v>
       </c>
       <c r="D59" s="1" t="str">
-        <v>dynamic heading added for nomiee</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-20</v>
       </c>
       <c r="B60" s="1">
         <v>158484</v>
       </c>
       <c r="C60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" s="1" t="str">
-        <v>Daily Scrum Call</v>
+        <v>dynamic heading added for nomiee</v>
       </c>
     </row>
     <row r="61">
@@ -1251,7 +1251,7 @@
         <v>158484</v>
       </c>
       <c r="C61" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" s="1" t="str">
         <v>Merge branch 'CR-36689-sgp' into smartGuaranteedPension-frontend</v>
@@ -1265,7 +1265,7 @@
         <v>158484</v>
       </c>
       <c r="C62" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" s="1" t="str">
         <v>Merge branch 'CR-36689-ytp' into youngTermPlan-frontend</v>
@@ -1279,7 +1279,7 @@
         <v>158484</v>
       </c>
       <c r="C63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" s="1" t="str">
         <v>Merge branch 'CR-36689-cpf' into promise4LifePlan-frontend</v>
@@ -1307,7 +1307,7 @@
         <v>158484</v>
       </c>
       <c r="C65" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D65" s="1" t="str">
         <v>Merge branch 'CR-36689-cpf' into promise4FuturePlan-frontend</v>
@@ -1335,7 +1335,7 @@
         <v>158484</v>
       </c>
       <c r="C67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" s="1" t="str">
         <v>Merge branch 'CR-36689-cpf' into titaniumPlusPlan-frontend</v>
